--- a/study_case_model/smaller_network/scenario_variables/price_scenarios152.xlsx
+++ b/study_case_model/smaller_network/scenario_variables/price_scenarios152.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.83007788797851</v>
+        <v>27.67372913579885</v>
       </c>
     </row>
     <row r="3">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>27.70240330505338</v>
+        <v>27.54677182581151</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>27.02919839834648</v>
+        <v>26.87734896914229</v>
       </c>
     </row>
     <row r="9">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>27.02596101859097</v>
+        <v>26.87412977691349</v>
       </c>
     </row>
     <row r="12">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>28.96332926714164</v>
+        <v>28.80061393418017</v>
       </c>
     </row>
     <row r="15">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>28.78813139834769</v>
+        <v>28.62640032307607</v>
       </c>
     </row>
     <row r="18">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.14805523394733</v>
+        <v>27.98992009218358</v>
       </c>
     </row>
     <row r="21">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>27.94364259423417</v>
+        <v>27.78665583808679</v>
       </c>
     </row>
     <row r="24">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>31.09859186559896</v>
+        <v>30.92388067534279</v>
       </c>
     </row>
     <row r="27">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>30.68605805877626</v>
+        <v>30.51366447417639</v>
       </c>
     </row>
     <row r="30">
